--- a/data/trans_camb/IP12-Dificultad-trans_camb.xlsx
+++ b/data/trans_camb/IP12-Dificultad-trans_camb.xlsx
@@ -40,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -66,13 +66,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin"/>
-      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
@@ -513,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K34"/>
+  <dimension ref="A1:H34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -524,9 +517,6 @@
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -542,68 +532,50 @@
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
-      <c r="E1" s="3" t="n"/>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Niña</t>
         </is>
       </c>
-      <c r="G1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
       <c r="H1" s="3" t="n"/>
-      <c r="I1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="J1" s="3" t="n"/>
-      <c r="K1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
       <c r="B2" s="2" t="n"/>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>2012/2007</t>
+          <t>2016/2012</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>2016/2007</t>
+          <t>2023/2012</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>2023/2007</t>
+          <t>2016/2012</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>2012/2007</t>
+          <t>2023/2012</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>2016/2007</t>
+          <t>2016/2012</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>2023/2007</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>2012/2007</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>2016/2007</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>2023/2007</t>
+          <t>2023/2012</t>
         </is>
       </c>
     </row>
@@ -616,9 +588,6 @@
       <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="n"/>
       <c r="H3" s="2" t="n"/>
-      <c r="I3" s="2" t="n"/>
-      <c r="J3" s="2" t="n"/>
-      <c r="K3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -631,15 +600,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr"/>
-      <c r="D4" s="5" t="inlineStr"/>
-      <c r="E4" s="5" t="inlineStr"/>
-      <c r="F4" s="5" t="inlineStr"/>
-      <c r="G4" s="5" t="inlineStr"/>
-      <c r="H4" s="5" t="inlineStr"/>
-      <c r="I4" s="5" t="inlineStr"/>
-      <c r="J4" s="5" t="inlineStr"/>
-      <c r="K4" s="5" t="inlineStr"/>
+      <c r="C4" s="5" t="n">
+        <v>-2.458891738479895</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-1.853702389839378</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.555437658485905</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>-0.04553332351955597</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>-1.01630791865214</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>-0.9940766758832431</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
@@ -648,15 +626,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr"/>
-      <c r="D5" s="5" t="inlineStr"/>
-      <c r="E5" s="5" t="inlineStr"/>
-      <c r="F5" s="5" t="inlineStr"/>
-      <c r="G5" s="5" t="inlineStr"/>
-      <c r="H5" s="5" t="inlineStr"/>
-      <c r="I5" s="5" t="inlineStr"/>
-      <c r="J5" s="5" t="inlineStr"/>
-      <c r="K5" s="5" t="inlineStr"/>
+      <c r="C5" s="5" t="n">
+        <v>-6.851107666543543</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-7.100803191318188</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-4.279605673511615</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-4.948526371028237</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>-4.122034727169333</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>-4.876269161139225</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
@@ -665,15 +652,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr"/>
-      <c r="D6" s="5" t="inlineStr"/>
-      <c r="E6" s="5" t="inlineStr"/>
-      <c r="F6" s="5" t="inlineStr"/>
-      <c r="G6" s="5" t="inlineStr"/>
-      <c r="H6" s="5" t="inlineStr"/>
-      <c r="I6" s="5" t="inlineStr"/>
-      <c r="J6" s="5" t="inlineStr"/>
-      <c r="K6" s="5" t="inlineStr"/>
+      <c r="C6" s="5" t="n">
+        <v>1.98827760432876</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>4.58618775643482</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>4.984113637934491</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>7.11117941868524</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>1.958020620628149</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>3.384315539099594</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n"/>
@@ -682,15 +678,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr"/>
-      <c r="D7" s="6" t="inlineStr"/>
-      <c r="E7" s="6" t="inlineStr"/>
-      <c r="F7" s="6" t="inlineStr"/>
-      <c r="G7" s="6" t="inlineStr"/>
-      <c r="H7" s="6" t="inlineStr"/>
-      <c r="I7" s="6" t="inlineStr"/>
-      <c r="J7" s="6" t="inlineStr"/>
-      <c r="K7" s="6" t="inlineStr"/>
+      <c r="C7" s="6" t="n">
+        <v>-0.2310462610043695</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>-0.1741805055850182</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>0.05615565027971517</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>-0.004603493033957115</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-0.09889746297710721</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.09673412894386663</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
@@ -699,15 +704,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr"/>
-      <c r="D8" s="6" t="inlineStr"/>
-      <c r="E8" s="6" t="inlineStr"/>
-      <c r="F8" s="6" t="inlineStr"/>
-      <c r="G8" s="6" t="inlineStr"/>
-      <c r="H8" s="6" t="inlineStr"/>
-      <c r="I8" s="6" t="inlineStr"/>
-      <c r="J8" s="6" t="inlineStr"/>
-      <c r="K8" s="6" t="inlineStr"/>
+      <c r="C8" s="6" t="n">
+        <v>-0.5261762594119553</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>-0.5878898397630268</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>-0.3563100112666502</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>-0.4585972585583373</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.3463331572862669</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.4296912394325516</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
@@ -716,15 +730,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr"/>
-      <c r="D9" s="6" t="inlineStr"/>
-      <c r="E9" s="6" t="inlineStr"/>
-      <c r="F9" s="6" t="inlineStr"/>
-      <c r="G9" s="6" t="inlineStr"/>
-      <c r="H9" s="6" t="inlineStr"/>
-      <c r="I9" s="6" t="inlineStr"/>
-      <c r="J9" s="6" t="inlineStr"/>
-      <c r="K9" s="6" t="inlineStr"/>
+      <c r="C9" s="6" t="n">
+        <v>0.2270569983821507</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>0.5287542569666555</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>0.6422557140600407</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>0.8768164914231511</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.238588550903129</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>0.3702544916988311</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -737,15 +760,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr"/>
-      <c r="D10" s="5" t="inlineStr"/>
-      <c r="E10" s="5" t="inlineStr"/>
-      <c r="F10" s="5" t="inlineStr"/>
-      <c r="G10" s="5" t="inlineStr"/>
-      <c r="H10" s="5" t="inlineStr"/>
-      <c r="I10" s="5" t="inlineStr"/>
-      <c r="J10" s="5" t="inlineStr"/>
-      <c r="K10" s="5" t="inlineStr"/>
+      <c r="C10" s="5" t="n">
+        <v>-3.114842462575224</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>2.429666812873908</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-0.485750119855119</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>-1.006879264299547</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>-1.806002573822353</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>0.8105167906136481</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
@@ -754,15 +786,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr"/>
-      <c r="D11" s="5" t="inlineStr"/>
-      <c r="E11" s="5" t="inlineStr"/>
-      <c r="F11" s="5" t="inlineStr"/>
-      <c r="G11" s="5" t="inlineStr"/>
-      <c r="H11" s="5" t="inlineStr"/>
-      <c r="I11" s="5" t="inlineStr"/>
-      <c r="J11" s="5" t="inlineStr"/>
-      <c r="K11" s="5" t="inlineStr"/>
+      <c r="C11" s="5" t="n">
+        <v>-7.396890980537096</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-2.331718899317975</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-4.60357441124271</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-5.493743196078462</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>-4.466802101244715</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>-2.249105708404988</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
@@ -771,15 +812,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr"/>
-      <c r="D12" s="5" t="inlineStr"/>
-      <c r="E12" s="5" t="inlineStr"/>
-      <c r="F12" s="5" t="inlineStr"/>
-      <c r="G12" s="5" t="inlineStr"/>
-      <c r="H12" s="5" t="inlineStr"/>
-      <c r="I12" s="5" t="inlineStr"/>
-      <c r="J12" s="5" t="inlineStr"/>
-      <c r="K12" s="5" t="inlineStr"/>
+      <c r="C12" s="5" t="n">
+        <v>0.3043110414531764</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>7.728227979225884</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>3.801063399030601</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>3.263986491931407</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>0.9975686597832054</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>4.280390312044609</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n"/>
@@ -788,15 +838,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr"/>
-      <c r="D13" s="6" t="inlineStr"/>
-      <c r="E13" s="6" t="inlineStr"/>
-      <c r="F13" s="6" t="inlineStr"/>
-      <c r="G13" s="6" t="inlineStr"/>
-      <c r="H13" s="6" t="inlineStr"/>
-      <c r="I13" s="6" t="inlineStr"/>
-      <c r="J13" s="6" t="inlineStr"/>
-      <c r="K13" s="6" t="inlineStr"/>
+      <c r="C13" s="6" t="n">
+        <v>-0.4068654491611215</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>0.3173667660593411</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>-0.06371345762777381</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>-0.1320674081590907</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.236392717418323</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>0.1060908048656995</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
@@ -805,15 +864,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr"/>
-      <c r="D14" s="6" t="inlineStr"/>
-      <c r="E14" s="6" t="inlineStr"/>
-      <c r="F14" s="6" t="inlineStr"/>
-      <c r="G14" s="6" t="inlineStr"/>
-      <c r="H14" s="6" t="inlineStr"/>
-      <c r="I14" s="6" t="inlineStr"/>
-      <c r="J14" s="6" t="inlineStr"/>
-      <c r="K14" s="6" t="inlineStr"/>
+      <c r="C14" s="6" t="n">
+        <v>-0.7026505272091151</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>-0.2685232907370843</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>-0.464879211713102</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>-0.5625427151220826</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.5037457705317522</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.2704486738138492</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
@@ -822,15 +890,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr"/>
-      <c r="D15" s="6" t="inlineStr"/>
-      <c r="E15" s="6" t="inlineStr"/>
-      <c r="F15" s="6" t="inlineStr"/>
-      <c r="G15" s="6" t="inlineStr"/>
-      <c r="H15" s="6" t="inlineStr"/>
-      <c r="I15" s="6" t="inlineStr"/>
-      <c r="J15" s="6" t="inlineStr"/>
-      <c r="K15" s="6" t="inlineStr"/>
+      <c r="C15" s="6" t="n">
+        <v>0.1112391899956292</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>1.332080392923252</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>0.7101445399152774</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>0.6326105535304589</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.1841392748100387</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.7006588173951938</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -843,15 +920,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr"/>
-      <c r="D16" s="5" t="inlineStr"/>
-      <c r="E16" s="5" t="inlineStr"/>
-      <c r="F16" s="5" t="inlineStr"/>
-      <c r="G16" s="5" t="inlineStr"/>
-      <c r="H16" s="5" t="inlineStr"/>
-      <c r="I16" s="5" t="inlineStr"/>
-      <c r="J16" s="5" t="inlineStr"/>
-      <c r="K16" s="5" t="inlineStr"/>
+      <c r="C16" s="5" t="n">
+        <v>-0.5503208923812883</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>-0.1127165344431996</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>-0.997903910948357</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>-1.905675488959257</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>-0.7767136535699035</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>-0.9254001520073524</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
@@ -860,15 +946,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr"/>
-      <c r="D17" s="5" t="inlineStr"/>
-      <c r="E17" s="5" t="inlineStr"/>
-      <c r="F17" s="5" t="inlineStr"/>
-      <c r="G17" s="5" t="inlineStr"/>
-      <c r="H17" s="5" t="inlineStr"/>
-      <c r="I17" s="5" t="inlineStr"/>
-      <c r="J17" s="5" t="inlineStr"/>
-      <c r="K17" s="5" t="inlineStr"/>
+      <c r="C17" s="5" t="n">
+        <v>-4.83675946222623</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-4.992354150964883</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-5.621520722264859</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-6.275182192832161</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>-3.805647515789258</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>-4.160167261945405</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
@@ -877,15 +972,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr"/>
-      <c r="D18" s="5" t="inlineStr"/>
-      <c r="E18" s="5" t="inlineStr"/>
-      <c r="F18" s="5" t="inlineStr"/>
-      <c r="G18" s="5" t="inlineStr"/>
-      <c r="H18" s="5" t="inlineStr"/>
-      <c r="I18" s="5" t="inlineStr"/>
-      <c r="J18" s="5" t="inlineStr"/>
-      <c r="K18" s="5" t="inlineStr"/>
+      <c r="C18" s="5" t="n">
+        <v>4.119455751309642</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>4.148926827790931</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>3.615142427258128</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>2.214468861253406</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>2.394332190655896</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>2.145646698212104</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n"/>
@@ -894,15 +998,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr"/>
-      <c r="D19" s="6" t="inlineStr"/>
-      <c r="E19" s="6" t="inlineStr"/>
-      <c r="F19" s="6" t="inlineStr"/>
-      <c r="G19" s="6" t="inlineStr"/>
-      <c r="H19" s="6" t="inlineStr"/>
-      <c r="I19" s="6" t="inlineStr"/>
-      <c r="J19" s="6" t="inlineStr"/>
-      <c r="K19" s="6" t="inlineStr"/>
+      <c r="C19" s="6" t="n">
+        <v>-0.08032338199748647</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>-0.01645180726164596</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>-0.143285911642755</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>-0.2736300025833961</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>-0.1124536689315499</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>-0.1339807042720861</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n"/>
@@ -911,15 +1024,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C20" s="6" t="inlineStr"/>
-      <c r="D20" s="6" t="inlineStr"/>
-      <c r="E20" s="6" t="inlineStr"/>
-      <c r="F20" s="6" t="inlineStr"/>
-      <c r="G20" s="6" t="inlineStr"/>
-      <c r="H20" s="6" t="inlineStr"/>
-      <c r="I20" s="6" t="inlineStr"/>
-      <c r="J20" s="6" t="inlineStr"/>
-      <c r="K20" s="6" t="inlineStr"/>
+      <c r="C20" s="6" t="n">
+        <v>-0.5577369934282703</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>-0.5216564418057931</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>-0.6090793460074985</v>
+      </c>
+      <c r="F20" s="6" t="n">
+        <v>-0.6315918150984825</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>-0.4492495693119504</v>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>-0.4623533404408144</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n"/>
@@ -928,15 +1050,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr"/>
-      <c r="D21" s="6" t="inlineStr"/>
-      <c r="E21" s="6" t="inlineStr"/>
-      <c r="F21" s="6" t="inlineStr"/>
-      <c r="G21" s="6" t="inlineStr"/>
-      <c r="H21" s="6" t="inlineStr"/>
-      <c r="I21" s="6" t="inlineStr"/>
-      <c r="J21" s="6" t="inlineStr"/>
-      <c r="K21" s="6" t="inlineStr"/>
+      <c r="C21" s="6" t="n">
+        <v>1.056443467490861</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>0.9570917317400983</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>0.8062435965356775</v>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>0.5259306702690876</v>
+      </c>
+      <c r="G21" s="6" t="n">
+        <v>0.4879631559977868</v>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>0.4205784846621218</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
@@ -949,15 +1080,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr"/>
-      <c r="D22" s="5" t="inlineStr"/>
-      <c r="E22" s="5" t="inlineStr"/>
-      <c r="F22" s="5" t="inlineStr"/>
-      <c r="G22" s="5" t="inlineStr"/>
-      <c r="H22" s="5" t="inlineStr"/>
-      <c r="I22" s="5" t="inlineStr"/>
-      <c r="J22" s="5" t="inlineStr"/>
-      <c r="K22" s="5" t="inlineStr"/>
+      <c r="C22" s="5" t="n">
+        <v>-0.182291091376606</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>0.1310669138809617</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>-4.563183953387089</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>-1.688787902380351</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>-2.154537367788222</v>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>-0.6219087097222895</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n"/>
@@ -966,15 +1106,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr"/>
-      <c r="D23" s="5" t="inlineStr"/>
-      <c r="E23" s="5" t="inlineStr"/>
-      <c r="F23" s="5" t="inlineStr"/>
-      <c r="G23" s="5" t="inlineStr"/>
-      <c r="H23" s="5" t="inlineStr"/>
-      <c r="I23" s="5" t="inlineStr"/>
-      <c r="J23" s="5" t="inlineStr"/>
-      <c r="K23" s="5" t="inlineStr"/>
+      <c r="C23" s="5" t="n">
+        <v>-6.279813716074313</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>-6.087916964766451</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>-11.84263117659067</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>-8.248449434004144</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>-6.713172236402221</v>
+      </c>
+      <c r="H23" s="5" t="n">
+        <v>-4.685096287205542</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n"/>
@@ -983,15 +1132,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr"/>
-      <c r="D24" s="5" t="inlineStr"/>
-      <c r="E24" s="5" t="inlineStr"/>
-      <c r="F24" s="5" t="inlineStr"/>
-      <c r="G24" s="5" t="inlineStr"/>
-      <c r="H24" s="5" t="inlineStr"/>
-      <c r="I24" s="5" t="inlineStr"/>
-      <c r="J24" s="5" t="inlineStr"/>
-      <c r="K24" s="5" t="inlineStr"/>
+      <c r="C24" s="5" t="n">
+        <v>5.349947861873237</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>5.644940379492044</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>1.769765047152179</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>5.000784482515682</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>2.548018022634795</v>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>3.944888418022386</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n"/>
@@ -1000,15 +1158,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C25" s="6" t="inlineStr"/>
-      <c r="D25" s="6" t="inlineStr"/>
-      <c r="E25" s="6" t="inlineStr"/>
-      <c r="F25" s="6" t="inlineStr"/>
-      <c r="G25" s="6" t="inlineStr"/>
-      <c r="H25" s="6" t="inlineStr"/>
-      <c r="I25" s="6" t="inlineStr"/>
-      <c r="J25" s="6" t="inlineStr"/>
-      <c r="K25" s="6" t="inlineStr"/>
+      <c r="C25" s="6" t="n">
+        <v>-0.02794597274043802</v>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>0.02009309601928661</v>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>-0.4500435750603532</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>-0.1665565431658275</v>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>-0.2640436824811255</v>
+      </c>
+      <c r="H25" s="6" t="n">
+        <v>-0.07621639259417085</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n"/>
@@ -1017,15 +1184,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C26" s="6" t="inlineStr"/>
-      <c r="D26" s="6" t="inlineStr"/>
-      <c r="E26" s="6" t="inlineStr"/>
-      <c r="F26" s="6" t="inlineStr"/>
-      <c r="G26" s="6" t="inlineStr"/>
-      <c r="H26" s="6" t="inlineStr"/>
-      <c r="I26" s="6" t="inlineStr"/>
-      <c r="J26" s="6" t="inlineStr"/>
-      <c r="K26" s="6" t="inlineStr"/>
+      <c r="C26" s="6" t="n">
+        <v>-0.678749413467026</v>
+      </c>
+      <c r="D26" s="6" t="n">
+        <v>-0.61544687019044</v>
+      </c>
+      <c r="E26" s="6" t="n">
+        <v>-0.7930757852095549</v>
+      </c>
+      <c r="F26" s="6" t="n">
+        <v>-0.5789903945145842</v>
+      </c>
+      <c r="G26" s="6" t="n">
+        <v>-0.6281596380846439</v>
+      </c>
+      <c r="H26" s="6" t="n">
+        <v>-0.443510190146956</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n"/>
@@ -1034,15 +1210,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C27" s="6" t="inlineStr"/>
-      <c r="D27" s="6" t="inlineStr"/>
-      <c r="E27" s="6" t="inlineStr"/>
-      <c r="F27" s="6" t="inlineStr"/>
-      <c r="G27" s="6" t="inlineStr"/>
-      <c r="H27" s="6" t="inlineStr"/>
-      <c r="I27" s="6" t="inlineStr"/>
-      <c r="J27" s="6" t="inlineStr"/>
-      <c r="K27" s="6" t="inlineStr"/>
+      <c r="C27" s="6" t="n">
+        <v>1.458687938704813</v>
+      </c>
+      <c r="D27" s="6" t="n">
+        <v>1.69040593668296</v>
+      </c>
+      <c r="E27" s="6" t="n">
+        <v>0.4076796069738465</v>
+      </c>
+      <c r="F27" s="6" t="n">
+        <v>0.9614219074360391</v>
+      </c>
+      <c r="G27" s="6" t="n">
+        <v>0.4581466936121683</v>
+      </c>
+      <c r="H27" s="6" t="n">
+        <v>0.6871413754360147</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
@@ -1055,15 +1240,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr"/>
-      <c r="D28" s="5" t="inlineStr"/>
-      <c r="E28" s="5" t="inlineStr"/>
-      <c r="F28" s="5" t="inlineStr"/>
-      <c r="G28" s="5" t="inlineStr"/>
-      <c r="H28" s="5" t="inlineStr"/>
-      <c r="I28" s="5" t="inlineStr"/>
-      <c r="J28" s="5" t="inlineStr"/>
-      <c r="K28" s="5" t="inlineStr"/>
+      <c r="C28" s="5" t="n">
+        <v>-1.804337353545994</v>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>-0.3307514467407208</v>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>-0.609608320990175</v>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>-1.537352572486657</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>-1.226013451545463</v>
+      </c>
+      <c r="H28" s="5" t="n">
+        <v>-0.8997535216635016</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n"/>
@@ -1072,15 +1266,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr"/>
-      <c r="D29" s="5" t="inlineStr"/>
-      <c r="E29" s="5" t="inlineStr"/>
-      <c r="F29" s="5" t="inlineStr"/>
-      <c r="G29" s="5" t="inlineStr"/>
-      <c r="H29" s="5" t="inlineStr"/>
-      <c r="I29" s="5" t="inlineStr"/>
-      <c r="J29" s="5" t="inlineStr"/>
-      <c r="K29" s="5" t="inlineStr"/>
+      <c r="C29" s="5" t="n">
+        <v>-4.220940593236054</v>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>-2.571357192154338</v>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>-2.929718671421132</v>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>-3.788071357762078</v>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>-2.897800552610459</v>
+      </c>
+      <c r="H29" s="5" t="n">
+        <v>-2.57288751351467</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n"/>
@@ -1089,15 +1292,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C30" s="5" t="inlineStr"/>
-      <c r="D30" s="5" t="inlineStr"/>
-      <c r="E30" s="5" t="inlineStr"/>
-      <c r="F30" s="5" t="inlineStr"/>
-      <c r="G30" s="5" t="inlineStr"/>
-      <c r="H30" s="5" t="inlineStr"/>
-      <c r="I30" s="5" t="inlineStr"/>
-      <c r="J30" s="5" t="inlineStr"/>
-      <c r="K30" s="5" t="inlineStr"/>
+      <c r="C30" s="5" t="n">
+        <v>0.3405631316334579</v>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>2.155316771213404</v>
+      </c>
+      <c r="E30" s="5" t="n">
+        <v>1.765104692947208</v>
+      </c>
+      <c r="F30" s="5" t="n">
+        <v>0.9222904290690439</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>0.323547890074234</v>
+      </c>
+      <c r="H30" s="5" t="n">
+        <v>0.86208943034231</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n"/>
@@ -1106,15 +1318,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C31" s="6" t="inlineStr"/>
-      <c r="D31" s="6" t="inlineStr"/>
-      <c r="E31" s="6" t="inlineStr"/>
-      <c r="F31" s="6" t="inlineStr"/>
-      <c r="G31" s="6" t="inlineStr"/>
-      <c r="H31" s="6" t="inlineStr"/>
-      <c r="I31" s="6" t="inlineStr"/>
-      <c r="J31" s="6" t="inlineStr"/>
-      <c r="K31" s="6" t="inlineStr"/>
+      <c r="C31" s="6" t="n">
+        <v>-0.2156111023993455</v>
+      </c>
+      <c r="D31" s="6" t="n">
+        <v>-0.03952347597958619</v>
+      </c>
+      <c r="E31" s="6" t="n">
+        <v>-0.07127078107670795</v>
+      </c>
+      <c r="F31" s="6" t="n">
+        <v>-0.1797356021214419</v>
+      </c>
+      <c r="G31" s="6" t="n">
+        <v>-0.144940862452765</v>
+      </c>
+      <c r="H31" s="6" t="n">
+        <v>-0.1063700004762832</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n"/>
@@ -1123,15 +1344,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C32" s="6" t="inlineStr"/>
-      <c r="D32" s="6" t="inlineStr"/>
-      <c r="E32" s="6" t="inlineStr"/>
-      <c r="F32" s="6" t="inlineStr"/>
-      <c r="G32" s="6" t="inlineStr"/>
-      <c r="H32" s="6" t="inlineStr"/>
-      <c r="I32" s="6" t="inlineStr"/>
-      <c r="J32" s="6" t="inlineStr"/>
-      <c r="K32" s="6" t="inlineStr"/>
+      <c r="C32" s="6" t="n">
+        <v>-0.4305555726412627</v>
+      </c>
+      <c r="D32" s="6" t="n">
+        <v>-0.2734330622832214</v>
+      </c>
+      <c r="E32" s="6" t="n">
+        <v>-0.2992922026729123</v>
+      </c>
+      <c r="F32" s="6" t="n">
+        <v>-0.388562714963039</v>
+      </c>
+      <c r="G32" s="6" t="n">
+        <v>-0.3059508093833124</v>
+      </c>
+      <c r="H32" s="6" t="n">
+        <v>-0.2764059424045217</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n"/>
@@ -1140,15 +1370,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C33" s="6" t="inlineStr"/>
-      <c r="D33" s="6" t="inlineStr"/>
-      <c r="E33" s="6" t="inlineStr"/>
-      <c r="F33" s="6" t="inlineStr"/>
-      <c r="G33" s="6" t="inlineStr"/>
-      <c r="H33" s="6" t="inlineStr"/>
-      <c r="I33" s="6" t="inlineStr"/>
-      <c r="J33" s="6" t="inlineStr"/>
-      <c r="K33" s="6" t="inlineStr"/>
+      <c r="C33" s="6" t="n">
+        <v>0.04916642468489846</v>
+      </c>
+      <c r="D33" s="6" t="n">
+        <v>0.2938628061363743</v>
+      </c>
+      <c r="E33" s="6" t="n">
+        <v>0.2430218160915388</v>
+      </c>
+      <c r="F33" s="6" t="n">
+        <v>0.1213616279506031</v>
+      </c>
+      <c r="G33" s="6" t="n">
+        <v>0.04987082134046289</v>
+      </c>
+      <c r="H33" s="6" t="n">
+        <v>0.1139990670466031</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1159,11 +1398,11 @@
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="C1:E1"/>
     <mergeCell ref="A22:A27"/>
     <mergeCell ref="A4:A9"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="E1:F1"/>
     <mergeCell ref="A16:A21"/>
     <mergeCell ref="A10:A15"/>
     <mergeCell ref="A28:A33"/>
